--- a/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/5_five_bus_radial_grid_1ph_ynyn_MP_pf_sc_results_0_branch.xlsx
+++ b/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/5_five_bus_radial_grid_1ph_ynyn_MP_pf_sc_results_0_branch.xlsx
@@ -876,40 +876,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-1.563194052505438E-14</v>
+        <v>-5.210646841688371E-15</v>
       </c>
       <c r="O2">
-        <v>5.210612506905471E-15</v>
+        <v>2.86585137790303E-14</v>
       </c>
       <c r="P2">
-        <v>-1.042134522547605E-14</v>
+        <v>-1.042133823105609E-14</v>
       </c>
       <c r="Q2">
-        <v>-1.168742183302731E-26</v>
+        <v>-5.210646841688372E-15</v>
       </c>
       <c r="R2">
-        <v>4.625822325666277E-19</v>
+        <v>-1.042082159623702E-14</v>
       </c>
       <c r="S2">
-        <v>5.211126632729633E-15</v>
+        <v>5.211119639142437E-15</v>
       </c>
       <c r="T2">
-        <v>1.042129368339491E-14</v>
+        <v>-5.885971638871058E-29</v>
       </c>
       <c r="U2">
-        <v>5.76340267785982E-09</v>
+        <v>5.763371413985828E-09</v>
       </c>
       <c r="V2">
-        <v>-5.76340268204086E-09</v>
+        <v>-5.763392260736157E-09</v>
       </c>
       <c r="W2">
-        <v>-1.042129368337738E-14</v>
+        <v>-6.02851878080757E-29</v>
       </c>
       <c r="X2">
-        <v>-5.763413098667596E-09</v>
+        <v>-5.763384440117026E-09</v>
       </c>
       <c r="Y2">
-        <v>5.763397471879912E-09</v>
+        <v>5.763392261222049E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -930,40 +930,40 @@
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.100000023808833</v>
+        <v>1.100000023808765</v>
       </c>
       <c r="AG2">
-        <v>0.5500000117050743</v>
+        <v>0.5500000117057467</v>
       </c>
       <c r="AH2">
-        <v>0.5500000121040698</v>
+        <v>0.5500000121030186</v>
       </c>
       <c r="AI2">
-        <v>1.100000023808833</v>
+        <v>1.100000023808766</v>
       </c>
       <c r="AJ2">
-        <v>0.5500000116587047</v>
+        <v>0.5500000116593771</v>
       </c>
       <c r="AK2">
-        <v>0.5500000121504387</v>
+        <v>0.5500000121493873</v>
       </c>
       <c r="AL2">
-        <v>-6.426806457872223E-11</v>
+        <v>6.472158706724486E-13</v>
       </c>
       <c r="AM2">
-        <v>-179.9999999996514</v>
+        <v>-179.9999999995569</v>
       </c>
       <c r="AN2">
-        <v>179.9999999994803</v>
+        <v>179.9999999995499</v>
       </c>
       <c r="AO2">
-        <v>-6.425689216393618E-11</v>
+        <v>6.628902194870144E-13</v>
       </c>
       <c r="AP2">
-        <v>-179.9999999953941</v>
+        <v>-179.9999999952996</v>
       </c>
       <c r="AQ2">
-        <v>179.999999995223</v>
+        <v>179.9999999952925</v>
       </c>
     </row>
   </sheetData>
@@ -1148,40 +1148,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-1.563194052512732E-14</v>
+        <v>-5.210646841703724E-15</v>
       </c>
       <c r="O2">
-        <v>-7.30780895735253E-10</v>
+        <v>-7.307878274282729E-10</v>
       </c>
       <c r="P2">
-        <v>-2.039303680054263E-09</v>
+        <v>-2.039312874428952E-09</v>
       </c>
       <c r="Q2">
-        <v>5.210646841698816E-15</v>
+        <v>-5.210646841703823E-15</v>
       </c>
       <c r="R2">
-        <v>7.307775320660387E-10</v>
+        <v>7.307832745152802E-10</v>
       </c>
       <c r="S2">
-        <v>2.039303680343281E-09</v>
+        <v>2.039317060830524E-09</v>
       </c>
       <c r="T2">
-        <v>-1.563194052510674E-14</v>
+        <v>-5.210646841703823E-15</v>
       </c>
       <c r="U2">
-        <v>5.822527737118346E-09</v>
+        <v>5.822479044920499E-09</v>
       </c>
       <c r="V2">
-        <v>-3.556074214008267E-09</v>
+        <v>-3.55606079584426E-09</v>
       </c>
       <c r="W2">
-        <v>-1.042129368341479E-14</v>
+        <v>5.210646841703724E-15</v>
       </c>
       <c r="X2">
-        <v>-5.822515266428158E-09</v>
+        <v>-5.822486961752823E-09</v>
       </c>
       <c r="Y2">
-        <v>3.556074214336191E-09</v>
+        <v>3.556059114193066E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1202,40 +1202,40 @@
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.100000023812419</v>
+        <v>1.100000023812017</v>
       </c>
       <c r="AG2">
-        <v>0.681668345862667</v>
+        <v>0.6816683458635717</v>
       </c>
       <c r="AH2">
-        <v>0.4761907155784637</v>
+        <v>0.4761907155780343</v>
       </c>
       <c r="AI2">
-        <v>1.100000023812419</v>
+        <v>1.100000023812017</v>
       </c>
       <c r="AJ2">
-        <v>0.6816683458290512</v>
+        <v>0.6816683458299564</v>
       </c>
       <c r="AK2">
-        <v>0.4761907156282101</v>
+        <v>0.4761907156277809</v>
       </c>
       <c r="AL2">
-        <v>-3.771338270142585E-11</v>
+        <v>5.449700077556687E-13</v>
       </c>
       <c r="AM2">
-        <v>-164.9034422584519</v>
+        <v>-164.9034422584274</v>
       </c>
       <c r="AN2">
-        <v>158.1097491654318</v>
+        <v>158.1097491654785</v>
       </c>
       <c r="AO2">
-        <v>-3.771914194167265E-11</v>
+        <v>5.389834518979273E-13</v>
       </c>
       <c r="AP2">
-        <v>-164.9034422552532</v>
+        <v>-164.9034422552288</v>
       </c>
       <c r="AQ2">
-        <v>158.1097491642076</v>
+        <v>158.1097491642544</v>
       </c>
     </row>
   </sheetData>
@@ -1420,40 +1420,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-1.563194052512732E-14</v>
+        <v>-1.563194052511142E-14</v>
       </c>
       <c r="O2">
-        <v>-7.30780895735253E-10</v>
+        <v>-7.307608564704167E-10</v>
       </c>
       <c r="P2">
-        <v>-2.039303680054263E-09</v>
+        <v>-2.039306184182963E-09</v>
       </c>
       <c r="Q2">
-        <v>5.210646841698816E-15</v>
+        <v>5.210646841703924E-15</v>
       </c>
       <c r="R2">
-        <v>7.307775320660387E-10</v>
+        <v>7.307631333604394E-10</v>
       </c>
       <c r="S2">
-        <v>2.039303680343281E-09</v>
+        <v>2.039304502492865E-09</v>
       </c>
       <c r="T2">
-        <v>-1.563194052510674E-14</v>
+        <v>1.04212936834074E-14</v>
       </c>
       <c r="U2">
-        <v>5.822527737118346E-09</v>
+        <v>5.82250304276891E-09</v>
       </c>
       <c r="V2">
-        <v>-3.556074214008267E-09</v>
+        <v>-3.556068345915053E-09</v>
       </c>
       <c r="W2">
-        <v>-1.042129368341479E-14</v>
+        <v>-1.563194052511127E-14</v>
       </c>
       <c r="X2">
-        <v>-5.822515266428158E-09</v>
+        <v>-5.82249908386086E-09</v>
       </c>
       <c r="Y2">
-        <v>3.556074214336191E-09</v>
+        <v>3.556064160130422E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1474,40 +1474,40 @@
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.100000023812419</v>
+        <v>1.100000023812017</v>
       </c>
       <c r="AG2">
-        <v>0.681668345862667</v>
+        <v>0.6816683458635712</v>
       </c>
       <c r="AH2">
-        <v>0.4761907155784637</v>
+        <v>0.4761907155780346</v>
       </c>
       <c r="AI2">
-        <v>1.100000023812419</v>
+        <v>1.100000023812017</v>
       </c>
       <c r="AJ2">
-        <v>0.6816683458290512</v>
+        <v>0.6816683458299556</v>
       </c>
       <c r="AK2">
-        <v>0.4761907156282101</v>
+        <v>0.4761907156277811</v>
       </c>
       <c r="AL2">
-        <v>-3.771338270142585E-11</v>
+        <v>5.285043060735871E-13</v>
       </c>
       <c r="AM2">
-        <v>-164.9034422584519</v>
+        <v>-164.9034422584275</v>
       </c>
       <c r="AN2">
-        <v>158.1097491654318</v>
+        <v>158.1097491654785</v>
       </c>
       <c r="AO2">
-        <v>-3.771914194167265E-11</v>
+        <v>5.457698891294192E-13</v>
       </c>
       <c r="AP2">
-        <v>-164.9034422552532</v>
+        <v>-164.9034422552288</v>
       </c>
       <c r="AQ2">
-        <v>158.1097491642076</v>
+        <v>158.1097491642543</v>
       </c>
     </row>
   </sheetData>
@@ -1692,40 +1692,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-6.868579779017895E-14</v>
+        <v>2.368475785867734E-15</v>
       </c>
       <c r="O2">
-        <v>2.960584599238137E-14</v>
+        <v>-5.921291769868794E-15</v>
       </c>
       <c r="P2">
-        <v>3.079007967600271E-14</v>
+        <v>-2.368578668651526E-15</v>
       </c>
       <c r="Q2">
-        <v>6.865703272943889E-26</v>
+        <v>-2.368475785867732E-15</v>
       </c>
       <c r="R2">
-        <v>2.369256639394537E-15</v>
+        <v>5.92197130247496E-15</v>
       </c>
       <c r="S2">
-        <v>7.850922383245711E-19</v>
+        <v>4.737733994034456E-15</v>
       </c>
       <c r="T2">
-        <v>-1.990811072506728E-25</v>
+        <v>9.473903143471415E-15</v>
       </c>
       <c r="U2">
-        <v>4.763154017614578E-09</v>
+        <v>4.763125595899952E-09</v>
       </c>
       <c r="V2">
-        <v>-4.76314217870796E-09</v>
+        <v>-4.763137441769622E-09</v>
       </c>
       <c r="W2">
-        <v>-2.368475785868244E-14</v>
+        <v>-9.473903143471416E-15</v>
       </c>
       <c r="X2">
-        <v>-4.763142174834066E-09</v>
+        <v>-4.763130332449956E-09</v>
       </c>
       <c r="Y2">
-        <v>4.763146916061085E-09</v>
+        <v>4.76313744217119E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1746,40 +1746,40 @@
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.000000000000523</v>
+        <v>1.000000000000357</v>
       </c>
       <c r="AG2">
-        <v>0.4999999998175085</v>
+        <v>0.499999999816962</v>
       </c>
       <c r="AH2">
-        <v>0.500000000182006</v>
+        <v>0.5000000001833954</v>
       </c>
       <c r="AI2">
-        <v>1.000000000000525</v>
+        <v>1.000000000000357</v>
       </c>
       <c r="AJ2">
-        <v>0.499999999775353</v>
+        <v>0.4999999997748085</v>
       </c>
       <c r="AK2">
-        <v>0.5000000002241579</v>
+        <v>0.5000000002255492</v>
       </c>
       <c r="AL2">
-        <v>1.660679149581829E-10</v>
+        <v>6.851139153394422E-13</v>
       </c>
       <c r="AM2">
-        <v>-179.9999999987739</v>
+        <v>-179.9999999987621</v>
       </c>
       <c r="AN2">
-        <v>179.999999998723</v>
+        <v>179.9999999987551</v>
       </c>
       <c r="AO2">
-        <v>1.66088175051627E-10</v>
+        <v>6.975623751185118E-13</v>
       </c>
       <c r="AP2">
-        <v>-179.9999999905998</v>
+        <v>-179.9999999905879</v>
       </c>
       <c r="AQ2">
-        <v>179.9999999905488</v>
+        <v>179.999999990581</v>
       </c>
     </row>
   </sheetData>
@@ -1964,40 +1964,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-6.868579779017895E-14</v>
+        <v>2.368475785867734E-15</v>
       </c>
       <c r="O2">
-        <v>2.960584599238137E-14</v>
+        <v>-5.921291769868794E-15</v>
       </c>
       <c r="P2">
-        <v>3.079007967600271E-14</v>
+        <v>-2.368578668651526E-15</v>
       </c>
       <c r="Q2">
-        <v>6.865703272943889E-26</v>
+        <v>-2.368475785867732E-15</v>
       </c>
       <c r="R2">
-        <v>2.369256639394537E-15</v>
+        <v>5.92197130247496E-15</v>
       </c>
       <c r="S2">
-        <v>7.850922383245711E-19</v>
+        <v>4.737733994034456E-15</v>
       </c>
       <c r="T2">
-        <v>-1.990811072506728E-25</v>
+        <v>9.473903143471415E-15</v>
       </c>
       <c r="U2">
-        <v>4.763154017614578E-09</v>
+        <v>4.763125595899952E-09</v>
       </c>
       <c r="V2">
-        <v>-4.76314217870796E-09</v>
+        <v>-4.763137441769622E-09</v>
       </c>
       <c r="W2">
-        <v>-2.368475785868244E-14</v>
+        <v>-9.473903143471416E-15</v>
       </c>
       <c r="X2">
-        <v>-4.763142174834066E-09</v>
+        <v>-4.763130332449956E-09</v>
       </c>
       <c r="Y2">
-        <v>4.763146916061085E-09</v>
+        <v>4.76313744217119E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -2018,40 +2018,40 @@
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.000000000000523</v>
+        <v>1.000000000000357</v>
       </c>
       <c r="AG2">
-        <v>0.4999999998175085</v>
+        <v>0.499999999816962</v>
       </c>
       <c r="AH2">
-        <v>0.500000000182006</v>
+        <v>0.5000000001833954</v>
       </c>
       <c r="AI2">
-        <v>1.000000000000525</v>
+        <v>1.000000000000357</v>
       </c>
       <c r="AJ2">
-        <v>0.499999999775353</v>
+        <v>0.4999999997748085</v>
       </c>
       <c r="AK2">
-        <v>0.5000000002241579</v>
+        <v>0.5000000002255492</v>
       </c>
       <c r="AL2">
-        <v>1.660679149581829E-10</v>
+        <v>6.851139153394422E-13</v>
       </c>
       <c r="AM2">
-        <v>-179.9999999987739</v>
+        <v>-179.9999999987621</v>
       </c>
       <c r="AN2">
-        <v>179.999999998723</v>
+        <v>179.9999999987551</v>
       </c>
       <c r="AO2">
-        <v>1.66088175051627E-10</v>
+        <v>6.975623751185118E-13</v>
       </c>
       <c r="AP2">
-        <v>-179.9999999905998</v>
+        <v>-179.9999999905879</v>
       </c>
       <c r="AQ2">
-        <v>179.9999999905488</v>
+        <v>179.999999990581</v>
       </c>
     </row>
   </sheetData>
@@ -2236,40 +2236,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-3.079018521647078E-14</v>
+        <v>4.736951571761483E-15</v>
       </c>
       <c r="O2">
-        <v>-5.559406193222033E-10</v>
+        <v>-5.559692390665715E-10</v>
       </c>
       <c r="P2">
-        <v>-1.551453081435021E-09</v>
+        <v>-1.551455810273796E-09</v>
       </c>
       <c r="Q2">
-        <v>4.736951571774699E-15</v>
+        <v>-7.105427357642248E-15</v>
       </c>
       <c r="R2">
-        <v>5.559623149546535E-10</v>
+        <v>5.559692737140355E-10</v>
       </c>
       <c r="S2">
-        <v>1.551466660384543E-09</v>
+        <v>1.551461630097729E-09</v>
       </c>
       <c r="T2">
-        <v>9.473903143470064E-15</v>
+        <v>4.724144531411673E-29</v>
       </c>
       <c r="U2">
-        <v>4.833162626268314E-09</v>
+        <v>4.833164536790245E-09</v>
       </c>
       <c r="V2">
-        <v>-3.10891332939591E-09</v>
+        <v>-3.108921088526098E-09</v>
       </c>
       <c r="W2">
-        <v>-7.105427357634904E-15</v>
+        <v>2.368475785880669E-15</v>
       </c>
       <c r="X2">
-        <v>-4.833154371145198E-09</v>
+        <v>-4.833158601062055E-09</v>
       </c>
       <c r="Y2">
-        <v>3.108908554218644E-09</v>
+        <v>3.108919042183558E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -2290,40 +2290,40 @@
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.000000000005946</v>
+        <v>1.000000000005802</v>
       </c>
       <c r="AG2">
-        <v>0.6078088903898764</v>
+        <v>0.6078088903891387</v>
       </c>
       <c r="AH2">
-        <v>0.4340870104133195</v>
+        <v>0.43408701041406</v>
       </c>
       <c r="AI2">
-        <v>1.000000000005947</v>
+        <v>1.000000000005802</v>
       </c>
       <c r="AJ2">
-        <v>0.6078088903615383</v>
+        <v>0.6078088903608012</v>
       </c>
       <c r="AK2">
-        <v>0.4340870104717734</v>
+        <v>0.4340870104725142</v>
       </c>
       <c r="AL2">
-        <v>1.009876193228099E-10</v>
+        <v>5.714087200579786E-13</v>
       </c>
       <c r="AM2">
-        <v>-166.2935793302727</v>
+        <v>-166.2935793302449</v>
       </c>
       <c r="AN2">
-        <v>160.6235536347066</v>
+        <v>160.6235536346806</v>
       </c>
       <c r="AO2">
-        <v>1.01021761985077E-10</v>
+        <v>5.79944030002794E-13</v>
       </c>
       <c r="AP2">
-        <v>-166.2935793242783</v>
+        <v>-166.2935793242505</v>
       </c>
       <c r="AQ2">
-        <v>160.6235536297154</v>
+        <v>160.6235536296895</v>
       </c>
     </row>
   </sheetData>
@@ -2508,40 +2508,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-3.079018521647078E-14</v>
+        <v>4.736951571761483E-15</v>
       </c>
       <c r="O2">
-        <v>-5.559406193222033E-10</v>
+        <v>-5.559692390665715E-10</v>
       </c>
       <c r="P2">
-        <v>-1.551453081435021E-09</v>
+        <v>-1.551455810273796E-09</v>
       </c>
       <c r="Q2">
-        <v>4.736951571774699E-15</v>
+        <v>-7.105427357642248E-15</v>
       </c>
       <c r="R2">
-        <v>5.559623149546535E-10</v>
+        <v>5.559692737140355E-10</v>
       </c>
       <c r="S2">
-        <v>1.551466660384543E-09</v>
+        <v>1.551461630097729E-09</v>
       </c>
       <c r="T2">
-        <v>9.473903143470064E-15</v>
+        <v>4.724144531411673E-29</v>
       </c>
       <c r="U2">
-        <v>4.833162626268314E-09</v>
+        <v>4.833164536790245E-09</v>
       </c>
       <c r="V2">
-        <v>-3.10891332939591E-09</v>
+        <v>-3.108921088526098E-09</v>
       </c>
       <c r="W2">
-        <v>-7.105427357634904E-15</v>
+        <v>2.368475785880669E-15</v>
       </c>
       <c r="X2">
-        <v>-4.833154371145198E-09</v>
+        <v>-4.833158601062055E-09</v>
       </c>
       <c r="Y2">
-        <v>3.108908554218644E-09</v>
+        <v>3.108919042183558E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -2562,40 +2562,40 @@
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.000000000005946</v>
+        <v>1.000000000005802</v>
       </c>
       <c r="AG2">
-        <v>0.6078088903898764</v>
+        <v>0.6078088903891387</v>
       </c>
       <c r="AH2">
-        <v>0.4340870104133195</v>
+        <v>0.43408701041406</v>
       </c>
       <c r="AI2">
-        <v>1.000000000005947</v>
+        <v>1.000000000005802</v>
       </c>
       <c r="AJ2">
-        <v>0.6078088903615383</v>
+        <v>0.6078088903608012</v>
       </c>
       <c r="AK2">
-        <v>0.4340870104717734</v>
+        <v>0.4340870104725142</v>
       </c>
       <c r="AL2">
-        <v>1.009876193228099E-10</v>
+        <v>5.714087200579786E-13</v>
       </c>
       <c r="AM2">
-        <v>-166.2935793302727</v>
+        <v>-166.2935793302449</v>
       </c>
       <c r="AN2">
-        <v>160.6235536347066</v>
+        <v>160.6235536346806</v>
       </c>
       <c r="AO2">
-        <v>1.01021761985077E-10</v>
+        <v>5.79944030002794E-13</v>
       </c>
       <c r="AP2">
-        <v>-166.2935793242783</v>
+        <v>-166.2935793242505</v>
       </c>
       <c r="AQ2">
-        <v>160.6235536297154</v>
+        <v>160.6235536296895</v>
       </c>
     </row>
   </sheetData>
@@ -2783,40 +2783,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-2.957778087471495E-09</v>
+        <v>-2.957784166025723E-09</v>
       </c>
       <c r="O2">
-        <v>-7.393922166811856E-10</v>
+        <v>-7.394441108955868E-10</v>
       </c>
       <c r="P2">
-        <v>-7.394968738302586E-10</v>
+        <v>-7.394158180921507E-10</v>
       </c>
       <c r="Q2">
-        <v>2.957782429931012E-09</v>
+        <v>2.95778373205893E-09</v>
       </c>
       <c r="R2">
-        <v>7.394423742164921E-10</v>
+        <v>7.394346516333896E-10</v>
       </c>
       <c r="S2">
-        <v>7.394409863809837E-10</v>
+        <v>7.394203307081298E-10</v>
       </c>
       <c r="T2">
-        <v>2.953149384637996E-14</v>
+        <v>1.389420099005793E-14</v>
       </c>
       <c r="U2">
-        <v>-3.842286452138952E-09</v>
+        <v>-3.842276466405528E-09</v>
       </c>
       <c r="V2">
-        <v>3.842270992790164E-09</v>
+        <v>3.842263192193031E-09</v>
       </c>
       <c r="W2">
-        <v>-3.477971689447957E-15</v>
+        <v>-7.814825065708713E-15</v>
       </c>
       <c r="X2">
-        <v>3.842267440032749E-09</v>
+        <v>3.842275947083526E-09</v>
       </c>
       <c r="Y2">
-        <v>-3.842272388906796E-09</v>
+        <v>-3.842262323679906E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -2837,40 +2837,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.3666666747203187</v>
+        <v>0.3666666746541447</v>
       </c>
       <c r="AH2">
-        <v>0.9701088348564688</v>
+        <v>0.9701088351760906</v>
       </c>
       <c r="AI2">
-        <v>0.9701088354030093</v>
+        <v>0.9701088350717374</v>
       </c>
       <c r="AJ2">
-        <v>0.3666666747517783</v>
+        <v>0.3666666746856048</v>
       </c>
       <c r="AK2">
-        <v>0.9701088348769669</v>
+        <v>0.9701088351965891</v>
       </c>
       <c r="AL2">
-        <v>0.9701088353884568</v>
+        <v>0.9701088350571843</v>
       </c>
       <c r="AM2">
-        <v>-8.707495311286885E-08</v>
+        <v>1.660607065742775E-08</v>
       </c>
       <c r="AN2">
-        <v>-100.8933946550004</v>
+        <v>-100.8933946492837</v>
       </c>
       <c r="AO2">
-        <v>100.8933946487826</v>
+        <v>100.8933946504708</v>
       </c>
       <c r="AP2">
-        <v>-8.149707480217712E-08</v>
+        <v>2.218385509061854E-08</v>
       </c>
       <c r="AQ2">
-        <v>-100.8933946557135</v>
+        <v>-100.8933946499968</v>
       </c>
       <c r="AR2">
-        <v>100.8933946498941</v>
+        <v>100.8933946515823</v>
       </c>
     </row>
   </sheetData>
@@ -3058,40 +3058,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-2.957778087471495E-09</v>
+        <v>-2.957769836746906E-09</v>
       </c>
       <c r="O2">
-        <v>-7.393922166811856E-10</v>
+        <v>-7.394489257318239E-10</v>
       </c>
       <c r="P2">
-        <v>-7.394968738302586E-10</v>
+        <v>-7.394031488756862E-10</v>
       </c>
       <c r="Q2">
-        <v>2.957782429931012E-09</v>
+        <v>2.957772442324103E-09</v>
       </c>
       <c r="R2">
-        <v>7.394423742164921E-10</v>
+        <v>7.394487086849837E-10</v>
       </c>
       <c r="S2">
-        <v>7.394409863809837E-10</v>
+        <v>7.39417555037877E-10</v>
       </c>
       <c r="T2">
-        <v>2.953149384637996E-14</v>
+        <v>1.736025028437009E-15</v>
       </c>
       <c r="U2">
-        <v>-3.842286452138952E-09</v>
+        <v>-3.842265010500612E-09</v>
       </c>
       <c r="V2">
-        <v>3.842270992790164E-09</v>
+        <v>3.842270310068987E-09</v>
       </c>
       <c r="W2">
-        <v>-3.477971689447957E-15</v>
+        <v>-2.604178231581078E-15</v>
       </c>
       <c r="X2">
-        <v>3.842267440032749E-09</v>
+        <v>3.842263882434464E-09</v>
       </c>
       <c r="Y2">
-        <v>-3.842272388906796E-09</v>
+        <v>-3.842272217226115E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -3112,40 +3112,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.3666666747203187</v>
+        <v>0.366666674654145</v>
       </c>
       <c r="AH2">
-        <v>0.9701088348564688</v>
+        <v>0.9701088351760906</v>
       </c>
       <c r="AI2">
-        <v>0.9701088354030093</v>
+        <v>0.9701088350717374</v>
       </c>
       <c r="AJ2">
-        <v>0.3666666747517783</v>
+        <v>0.3666666746856049</v>
       </c>
       <c r="AK2">
-        <v>0.9701088348769669</v>
+        <v>0.9701088351965894</v>
       </c>
       <c r="AL2">
-        <v>0.9701088353884568</v>
+        <v>0.9701088350571839</v>
       </c>
       <c r="AM2">
-        <v>-8.707495311286885E-08</v>
+        <v>1.660607329143931E-08</v>
       </c>
       <c r="AN2">
-        <v>-100.8933946550004</v>
+        <v>-100.8933946492837</v>
       </c>
       <c r="AO2">
-        <v>100.8933946487826</v>
+        <v>100.8933946504708</v>
       </c>
       <c r="AP2">
-        <v>-8.149707480217712E-08</v>
+        <v>2.218377054367867E-08</v>
       </c>
       <c r="AQ2">
-        <v>-100.8933946557135</v>
+        <v>-100.8933946499968</v>
       </c>
       <c r="AR2">
-        <v>100.8933946498941</v>
+        <v>100.8933946515824</v>
       </c>
     </row>
   </sheetData>
@@ -3333,40 +3333,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-3.138968257467121E-09</v>
+        <v>-3.138988869437681E-09</v>
       </c>
       <c r="O2">
-        <v>-1.398944536540611E-09</v>
+        <v>-1.398922597874564E-09</v>
       </c>
       <c r="P2">
-        <v>-1.705493046927273E-10</v>
+        <v>-1.705560035248667E-10</v>
       </c>
       <c r="Q2">
-        <v>3.138982056821638E-09</v>
+        <v>3.138990674202989E-09</v>
       </c>
       <c r="R2">
-        <v>1.398927466123054E-09</v>
+        <v>1.398917664436686E-09</v>
       </c>
       <c r="S2">
-        <v>1.705483321037338E-10</v>
+        <v>1.705631888402904E-10</v>
       </c>
       <c r="T2">
-        <v>1.418397127804707E-09</v>
+        <v>1.418402592587717E-09</v>
       </c>
       <c r="U2">
-        <v>-2.221744607281681E-09</v>
+        <v>-2.221742621026704E-09</v>
       </c>
       <c r="V2">
-        <v>2.930946256106455E-09</v>
+        <v>2.930933793906068E-09</v>
       </c>
       <c r="W2">
-        <v>-1.418395304299753E-09</v>
+        <v>-1.418393227885748E-09</v>
       </c>
       <c r="X2">
-        <v>2.221729151954733E-09</v>
+        <v>2.221745480667542E-09</v>
       </c>
       <c r="Y2">
-        <v>-2.930925654609176E-09</v>
+        <v>-2.930931632818367E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -3387,40 +3387,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.6194744499872341</v>
+        <v>0.6194744497695827</v>
       </c>
       <c r="AH2">
-        <v>0.9443347708459234</v>
+        <v>0.94433477094435</v>
       </c>
       <c r="AI2">
-        <v>1.055985897846282</v>
+        <v>1.05598589769414</v>
       </c>
       <c r="AJ2">
-        <v>0.619474449996864</v>
+        <v>0.6194744497792128</v>
       </c>
       <c r="AK2">
-        <v>0.9443347708621118</v>
+        <v>0.944334770960538</v>
       </c>
       <c r="AL2">
-        <v>1.05598589783463</v>
+        <v>1.055985897682488</v>
       </c>
       <c r="AM2">
-        <v>-10.90775019980413</v>
+        <v>-10.90775017850474</v>
       </c>
       <c r="AN2">
-        <v>-108.7881138116985</v>
+        <v>-108.7881138042144</v>
       </c>
       <c r="AO2">
-        <v>106.739237119203</v>
+        <v>106.7392371168768</v>
       </c>
       <c r="AP2">
-        <v>-10.90775019690437</v>
+        <v>-10.90775017560495</v>
       </c>
       <c r="AQ2">
-        <v>-108.7881138118575</v>
+        <v>-108.7881138043734</v>
       </c>
       <c r="AR2">
-        <v>106.7392371198291</v>
+        <v>106.7392371175029</v>
       </c>
     </row>
   </sheetData>
@@ -3724,40 +3724,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-3.138968257467121E-09</v>
+        <v>-3.138981587154905E-09</v>
       </c>
       <c r="O2">
-        <v>-1.398944536540611E-09</v>
+        <v>-1.398925392087118E-09</v>
       </c>
       <c r="P2">
-        <v>-1.705493046927273E-10</v>
+        <v>-1.705497726323511E-10</v>
       </c>
       <c r="Q2">
-        <v>3.138982056821638E-09</v>
+        <v>3.138982559007263E-09</v>
       </c>
       <c r="R2">
-        <v>1.398927466123054E-09</v>
+        <v>1.398931722691565E-09</v>
       </c>
       <c r="S2">
-        <v>1.705483321037338E-10</v>
+        <v>1.705545628526824E-10</v>
       </c>
       <c r="T2">
-        <v>1.418397127804707E-09</v>
+        <v>1.41838998267551E-09</v>
       </c>
       <c r="U2">
-        <v>-2.221744607281681E-09</v>
+        <v>-2.221736945409487E-09</v>
       </c>
       <c r="V2">
-        <v>2.930946256106455E-09</v>
+        <v>2.930930444418213E-09</v>
       </c>
       <c r="W2">
-        <v>-1.418395304299753E-09</v>
+        <v>-1.418384940080536E-09</v>
       </c>
       <c r="X2">
-        <v>2.221729151954733E-09</v>
+        <v>2.221731248028448E-09</v>
       </c>
       <c r="Y2">
-        <v>-2.930925654609176E-09</v>
+        <v>-2.930929003681678E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -3778,40 +3778,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.6194744499872341</v>
+        <v>0.619474449769583</v>
       </c>
       <c r="AH2">
-        <v>0.9443347708459234</v>
+        <v>0.9443347709443498</v>
       </c>
       <c r="AI2">
-        <v>1.055985897846282</v>
+        <v>1.05598589769414</v>
       </c>
       <c r="AJ2">
-        <v>0.619474449996864</v>
+        <v>0.6194744497792132</v>
       </c>
       <c r="AK2">
-        <v>0.9443347708621118</v>
+        <v>0.9443347709605382</v>
       </c>
       <c r="AL2">
-        <v>1.05598589783463</v>
+        <v>1.055985897682488</v>
       </c>
       <c r="AM2">
-        <v>-10.90775019980413</v>
+        <v>-10.90775017850473</v>
       </c>
       <c r="AN2">
-        <v>-108.7881138116985</v>
+        <v>-108.7881138042144</v>
       </c>
       <c r="AO2">
-        <v>106.739237119203</v>
+        <v>106.7392371168768</v>
       </c>
       <c r="AP2">
-        <v>-10.90775019690437</v>
+        <v>-10.90775017560497</v>
       </c>
       <c r="AQ2">
-        <v>-108.7881138118575</v>
+        <v>-108.7881138043734</v>
       </c>
       <c r="AR2">
-        <v>106.7392371198291</v>
+        <v>106.7392371175029</v>
       </c>
     </row>
   </sheetData>
@@ -3999,40 +3999,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-2.444439120618849E-09</v>
+        <v>-2.444444251934605E-09</v>
       </c>
       <c r="O2">
-        <v>-6.1105968539285E-10</v>
+        <v>-6.111039826094426E-10</v>
       </c>
       <c r="P2">
-        <v>-6.111519876018384E-10</v>
+        <v>-6.111117537891441E-10</v>
       </c>
       <c r="Q2">
-        <v>2.444437542037697E-09</v>
+        <v>2.444445041829221E-09</v>
       </c>
       <c r="R2">
-        <v>6.11109346799434E-10</v>
+        <v>6.111027597570335E-10</v>
       </c>
       <c r="S2">
-        <v>6.111048110179269E-10</v>
+        <v>6.111109643978879E-10</v>
       </c>
       <c r="T2">
-        <v>1.539863137905326E-14</v>
+        <v>-1.579338047669959E-15</v>
       </c>
       <c r="U2">
-        <v>-3.175435585448383E-09</v>
+        <v>-3.175428124966566E-09</v>
       </c>
       <c r="V2">
-        <v>3.175417823648713E-09</v>
+        <v>3.175429819918895E-09</v>
       </c>
       <c r="W2">
-        <v>-3.980467566960603E-16</v>
+        <v>1.974321978155491E-15</v>
       </c>
       <c r="X2">
-        <v>3.175422837491446E-09</v>
+        <v>3.175427296818941E-09</v>
       </c>
       <c r="Y2">
-        <v>-3.175426902746407E-09</v>
+        <v>-3.175425717539006E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -4053,40 +4053,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.3333333333829271</v>
+        <v>0.3333333333308631</v>
       </c>
       <c r="AH2">
-        <v>0.8819171034522442</v>
+        <v>0.8819171037085272</v>
       </c>
       <c r="AI2">
-        <v>0.8819171039259344</v>
+        <v>0.881917103661102</v>
       </c>
       <c r="AJ2">
-        <v>0.3333333334378387</v>
+        <v>0.3333333333857751</v>
       </c>
       <c r="AK2">
-        <v>0.8819171034733643</v>
+        <v>0.8819171037296486</v>
       </c>
       <c r="AL2">
-        <v>0.8819171039151917</v>
+        <v>0.881917103650358</v>
       </c>
       <c r="AM2">
-        <v>-8.294602442933605E-08</v>
+        <v>8.301934956203268E-09</v>
       </c>
       <c r="AN2">
-        <v>-100.8933946538112</v>
+        <v>-100.8933946487908</v>
       </c>
       <c r="AO2">
-        <v>100.8933946478895</v>
+        <v>100.8933946493849</v>
       </c>
       <c r="AP2">
-        <v>-7.736809076119025E-08</v>
+        <v>1.387965595431468E-08</v>
       </c>
       <c r="AQ2">
-        <v>-100.8933946553637</v>
+        <v>-100.8933946503432</v>
       </c>
       <c r="AR2">
-        <v>100.8933946498403</v>
+        <v>100.8933946513357</v>
       </c>
     </row>
   </sheetData>
@@ -4274,40 +4274,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-2.444439120618849E-09</v>
+        <v>-2.444444251934605E-09</v>
       </c>
       <c r="O2">
-        <v>-6.1105968539285E-10</v>
+        <v>-6.111039826094426E-10</v>
       </c>
       <c r="P2">
-        <v>-6.111519876018384E-10</v>
+        <v>-6.111117537891441E-10</v>
       </c>
       <c r="Q2">
-        <v>2.444437542037697E-09</v>
+        <v>2.444445041829221E-09</v>
       </c>
       <c r="R2">
-        <v>6.11109346799434E-10</v>
+        <v>6.111027597570335E-10</v>
       </c>
       <c r="S2">
-        <v>6.111048110179269E-10</v>
+        <v>6.111109643978879E-10</v>
       </c>
       <c r="T2">
-        <v>1.539863137905326E-14</v>
+        <v>-1.579338047669959E-15</v>
       </c>
       <c r="U2">
-        <v>-3.175435585448383E-09</v>
+        <v>-3.175428124966566E-09</v>
       </c>
       <c r="V2">
-        <v>3.175417823648713E-09</v>
+        <v>3.175429819918895E-09</v>
       </c>
       <c r="W2">
-        <v>-3.980467566960603E-16</v>
+        <v>1.974321978155491E-15</v>
       </c>
       <c r="X2">
-        <v>3.175422837491446E-09</v>
+        <v>3.175427296818941E-09</v>
       </c>
       <c r="Y2">
-        <v>-3.175426902746407E-09</v>
+        <v>-3.175425717539006E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -4328,40 +4328,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.3333333333829271</v>
+        <v>0.3333333333308631</v>
       </c>
       <c r="AH2">
-        <v>0.8819171034522442</v>
+        <v>0.8819171037085272</v>
       </c>
       <c r="AI2">
-        <v>0.8819171039259344</v>
+        <v>0.881917103661102</v>
       </c>
       <c r="AJ2">
-        <v>0.3333333334378387</v>
+        <v>0.3333333333857751</v>
       </c>
       <c r="AK2">
-        <v>0.8819171034733643</v>
+        <v>0.8819171037296486</v>
       </c>
       <c r="AL2">
-        <v>0.8819171039151917</v>
+        <v>0.881917103650358</v>
       </c>
       <c r="AM2">
-        <v>-8.294602442933605E-08</v>
+        <v>8.301934956203268E-09</v>
       </c>
       <c r="AN2">
-        <v>-100.8933946538112</v>
+        <v>-100.8933946487908</v>
       </c>
       <c r="AO2">
-        <v>100.8933946478895</v>
+        <v>100.8933946493849</v>
       </c>
       <c r="AP2">
-        <v>-7.736809076119025E-08</v>
+        <v>1.387965595431468E-08</v>
       </c>
       <c r="AQ2">
-        <v>-100.8933946553637</v>
+        <v>-100.8933946503432</v>
       </c>
       <c r="AR2">
-        <v>100.8933946498403</v>
+        <v>100.8933946513357</v>
       </c>
     </row>
   </sheetData>
@@ -4549,40 +4549,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-2.624742177354712E-09</v>
+        <v>-2.624754625294521E-09</v>
       </c>
       <c r="O2">
-        <v>-1.140130410374043E-09</v>
+        <v>-1.140201870073222E-09</v>
       </c>
       <c r="P2">
-        <v>-1.722658178409873E-10</v>
+        <v>-1.721795167607302E-10</v>
       </c>
       <c r="Q2">
-        <v>2.62475423594822E-09</v>
+        <v>2.624761322193926E-09</v>
       </c>
       <c r="R2">
-        <v>1.140200982454443E-09</v>
+        <v>1.140202481388837E-09</v>
       </c>
       <c r="S2">
-        <v>1.721745432622922E-10</v>
+        <v>1.721806025618301E-10</v>
       </c>
       <c r="T2">
-        <v>1.117825205890233E-09</v>
+        <v>1.117780518312977E-09</v>
       </c>
       <c r="U2">
-        <v>-1.947098410507566E-09</v>
+        <v>-1.947071864500726E-09</v>
       </c>
       <c r="V2">
-        <v>2.5059475486449E-09</v>
+        <v>2.505958484767136E-09</v>
       </c>
       <c r="W2">
-        <v>-1.117779137887827E-09</v>
+        <v>-1.117783103251901E-09</v>
       </c>
       <c r="X2">
-        <v>1.947059333248664E-09</v>
+        <v>1.947077006920961E-09</v>
       </c>
       <c r="Y2">
-        <v>-2.505957574919972E-09</v>
+        <v>-2.505958169401563E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -4603,40 +4603,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.5421614593291995</v>
+        <v>0.5421614591499192</v>
       </c>
       <c r="AH2">
-        <v>0.8576025462241053</v>
+        <v>0.8576025463155462</v>
       </c>
       <c r="AI2">
-        <v>0.9547184907987699</v>
+        <v>0.954718490665963</v>
       </c>
       <c r="AJ2">
-        <v>0.5421614593563266</v>
+        <v>0.5421614591770476</v>
       </c>
       <c r="AK2">
-        <v>0.8576025462441051</v>
+        <v>0.8576025463355481</v>
       </c>
       <c r="AL2">
-        <v>0.954718490788508</v>
+        <v>0.9547184906556987</v>
       </c>
       <c r="AM2">
-        <v>-10.80277171599012</v>
+        <v>-10.80277169403305</v>
       </c>
       <c r="AN2">
-        <v>-108.0887396225805</v>
+        <v>-108.0887396155923</v>
       </c>
       <c r="AO2">
-        <v>106.1949204579421</v>
+        <v>106.1949204558219</v>
       </c>
       <c r="AP2">
-        <v>-10.80277171209445</v>
+        <v>-10.8027716901376</v>
       </c>
       <c r="AQ2">
-        <v>-108.0887396233234</v>
+        <v>-108.0887396163351</v>
       </c>
       <c r="AR2">
-        <v>106.1949204591695</v>
+        <v>106.1949204570494</v>
       </c>
     </row>
   </sheetData>
@@ -4824,40 +4824,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-2.624742177354712E-09</v>
+        <v>-2.624754625294521E-09</v>
       </c>
       <c r="O2">
-        <v>-1.140130410374043E-09</v>
+        <v>-1.140201870073222E-09</v>
       </c>
       <c r="P2">
-        <v>-1.722658178409873E-10</v>
+        <v>-1.721795167607302E-10</v>
       </c>
       <c r="Q2">
-        <v>2.62475423594822E-09</v>
+        <v>2.624761322193926E-09</v>
       </c>
       <c r="R2">
-        <v>1.140200982454443E-09</v>
+        <v>1.140202481388837E-09</v>
       </c>
       <c r="S2">
-        <v>1.721745432622922E-10</v>
+        <v>1.721806025618301E-10</v>
       </c>
       <c r="T2">
-        <v>1.117825205890233E-09</v>
+        <v>1.117780518312977E-09</v>
       </c>
       <c r="U2">
-        <v>-1.947098410507566E-09</v>
+        <v>-1.947071864500726E-09</v>
       </c>
       <c r="V2">
-        <v>2.5059475486449E-09</v>
+        <v>2.505958484767136E-09</v>
       </c>
       <c r="W2">
-        <v>-1.117779137887827E-09</v>
+        <v>-1.117783103251901E-09</v>
       </c>
       <c r="X2">
-        <v>1.947059333248664E-09</v>
+        <v>1.947077006920961E-09</v>
       </c>
       <c r="Y2">
-        <v>-2.505957574919972E-09</v>
+        <v>-2.505958169401563E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -4878,40 +4878,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.5421614593291995</v>
+        <v>0.5421614591499192</v>
       </c>
       <c r="AH2">
-        <v>0.8576025462241053</v>
+        <v>0.8576025463155462</v>
       </c>
       <c r="AI2">
-        <v>0.9547184907987699</v>
+        <v>0.954718490665963</v>
       </c>
       <c r="AJ2">
-        <v>0.5421614593563266</v>
+        <v>0.5421614591770476</v>
       </c>
       <c r="AK2">
-        <v>0.8576025462441051</v>
+        <v>0.8576025463355481</v>
       </c>
       <c r="AL2">
-        <v>0.954718490788508</v>
+        <v>0.9547184906556987</v>
       </c>
       <c r="AM2">
-        <v>-10.80277171599012</v>
+        <v>-10.80277169403305</v>
       </c>
       <c r="AN2">
-        <v>-108.0887396225805</v>
+        <v>-108.0887396155923</v>
       </c>
       <c r="AO2">
-        <v>106.1949204579421</v>
+        <v>106.1949204558219</v>
       </c>
       <c r="AP2">
-        <v>-10.80277171209445</v>
+        <v>-10.8027716901376</v>
       </c>
       <c r="AQ2">
-        <v>-108.0887396233234</v>
+        <v>-108.0887396163351</v>
       </c>
       <c r="AR2">
-        <v>106.1949204591695</v>
+        <v>106.1949204570494</v>
       </c>
     </row>
   </sheetData>
@@ -5099,40 +5099,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-2.957712519441815E-09</v>
+        <v>-2.957788941993869E-09</v>
       </c>
       <c r="O2">
-        <v>-7.394689427730647E-10</v>
+        <v>-7.394515773569512E-10</v>
       </c>
       <c r="P2">
-        <v>-7.394811085330611E-10</v>
+        <v>-7.394533148874869E-10</v>
       </c>
       <c r="Q2">
-        <v>2.957785468561067E-09</v>
+        <v>2.957781994528191E-09</v>
       </c>
       <c r="R2">
-        <v>7.394498375120942E-10</v>
+        <v>7.394533146833394E-10</v>
       </c>
       <c r="S2">
-        <v>7.394394238023951E-10</v>
+        <v>7.394428940379048E-10</v>
       </c>
       <c r="T2">
-        <v>3.126649393245083E-14</v>
+        <v>3.473687946081456E-15</v>
       </c>
       <c r="U2">
-        <v>3.842259767627547E-09</v>
+        <v>3.842254555968536E-09</v>
       </c>
       <c r="V2">
-        <v>-3.842289297754604E-09</v>
+        <v>-3.842247612875913E-09</v>
       </c>
       <c r="W2">
-        <v>-3.476305520755273E-15</v>
+        <v>-6.94738052243967E-15</v>
       </c>
       <c r="X2">
-        <v>-3.842268451535046E-09</v>
+        <v>-3.842254555464645E-09</v>
       </c>
       <c r="Y2">
-        <v>3.84226845567117E-09</v>
+        <v>3.842261508438059E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -5153,40 +5153,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.7333333492612319</v>
+        <v>0.7333333491947056</v>
       </c>
       <c r="AH2">
-        <v>0.3666666744202977</v>
+        <v>0.3666666743874889</v>
       </c>
       <c r="AI2">
-        <v>0.3666666748424805</v>
+        <v>0.3666666748072243</v>
       </c>
       <c r="AJ2">
-        <v>0.7333333492769607</v>
+        <v>0.7333333492104355</v>
       </c>
       <c r="AK2">
-        <v>0.3666666743817947</v>
+        <v>0.366666674348985</v>
       </c>
       <c r="AL2">
-        <v>0.3666666748967161</v>
+        <v>0.3666666748614584</v>
       </c>
       <c r="AM2">
-        <v>-5.061580294089442E-08</v>
+        <v>1.484120651845077E-09</v>
       </c>
       <c r="AN2">
-        <v>179.9999999493391</v>
+        <v>-179.9999999988592</v>
       </c>
       <c r="AO2">
-        <v>179.9999999502502</v>
+        <v>-179.9999999981704</v>
       </c>
       <c r="AP2">
-        <v>-4.922136677601435E-08</v>
+        <v>2.878557156384499E-09</v>
       </c>
       <c r="AQ2">
-        <v>179.9999999571196</v>
+        <v>-179.9999999910787</v>
       </c>
       <c r="AR2">
-        <v>179.9999999452587</v>
+        <v>179.9999999968235</v>
       </c>
     </row>
   </sheetData>
@@ -5374,40 +5374,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-2.957712519441815E-09</v>
+        <v>-2.957785468229308E-09</v>
       </c>
       <c r="O2">
-        <v>-7.394689427730647E-10</v>
+        <v>-7.394289978873103E-10</v>
       </c>
       <c r="P2">
-        <v>-7.394811085330611E-10</v>
+        <v>-7.394428935937983E-10</v>
       </c>
       <c r="Q2">
-        <v>2.957785468561067E-09</v>
+        <v>2.957778520763631E-09</v>
       </c>
       <c r="R2">
-        <v>7.394498375120942E-10</v>
+        <v>7.39437682742815E-10</v>
       </c>
       <c r="S2">
-        <v>7.394394238023951E-10</v>
+        <v>7.394394202733456E-10</v>
       </c>
       <c r="T2">
-        <v>3.126649393245083E-14</v>
+        <v>1.389498163108959E-14</v>
       </c>
       <c r="U2">
-        <v>3.842259767627547E-09</v>
+        <v>3.842264977262214E-09</v>
       </c>
       <c r="V2">
-        <v>-3.842289297754604E-09</v>
+        <v>-3.842268455463292E-09</v>
       </c>
       <c r="W2">
-        <v>-3.476305520755273E-15</v>
+        <v>-1.389490964590434E-14</v>
       </c>
       <c r="X2">
-        <v>-3.842268451535046E-09</v>
+        <v>-3.8422580292292E-09</v>
       </c>
       <c r="Y2">
-        <v>3.84226845567117E-09</v>
+        <v>3.842261508438057E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -5428,40 +5428,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.7333333492612319</v>
+        <v>0.7333333491947056</v>
       </c>
       <c r="AH2">
-        <v>0.3666666744202977</v>
+        <v>0.3666666743874888</v>
       </c>
       <c r="AI2">
-        <v>0.3666666748424805</v>
+        <v>0.3666666748072244</v>
       </c>
       <c r="AJ2">
-        <v>0.7333333492769607</v>
+        <v>0.7333333492104358</v>
       </c>
       <c r="AK2">
-        <v>0.3666666743817947</v>
+        <v>0.3666666743489844</v>
       </c>
       <c r="AL2">
-        <v>0.3666666748967161</v>
+        <v>0.3666666748614583</v>
       </c>
       <c r="AM2">
-        <v>-5.061580294089442E-08</v>
+        <v>1.48408772670039E-09</v>
       </c>
       <c r="AN2">
-        <v>179.9999999493391</v>
+        <v>-179.9999999988593</v>
       </c>
       <c r="AO2">
-        <v>179.9999999502502</v>
+        <v>-179.9999999981704</v>
       </c>
       <c r="AP2">
-        <v>-4.922136677601435E-08</v>
+        <v>2.878537872709875E-09</v>
       </c>
       <c r="AQ2">
-        <v>179.9999999571196</v>
+        <v>-179.9999999910789</v>
       </c>
       <c r="AR2">
-        <v>179.9999999452587</v>
+        <v>179.9999999968234</v>
       </c>
     </row>
   </sheetData>
@@ -5649,40 +5649,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-2.272224128705642E-09</v>
+        <v>-2.272194893776093E-09</v>
       </c>
       <c r="O2">
-        <v>-1.904113527250953E-09</v>
+        <v>-1.904149228854585E-09</v>
       </c>
       <c r="P2">
-        <v>-3.132498569241518E-09</v>
+        <v>-3.13250313307189E-09</v>
       </c>
       <c r="Q2">
-        <v>2.272189102692272E-09</v>
+        <v>2.272191403055787E-09</v>
       </c>
       <c r="R2">
-        <v>1.904149155420491E-09</v>
+        <v>1.904143740392306E-09</v>
       </c>
       <c r="S2">
-        <v>3.132505077898054E-09</v>
+        <v>3.132501831593808E-09</v>
       </c>
       <c r="T2">
-        <v>7.092213860288419E-10</v>
+        <v>7.092031188095123E-10</v>
       </c>
       <c r="U2">
-        <v>4.349328944866132E-09</v>
+        <v>4.349308002503501E-09</v>
       </c>
       <c r="V2">
-        <v>-8.033627840488352E-10</v>
+        <v>-8.033370921766452E-10</v>
       </c>
       <c r="W2">
-        <v>-7.091986571270121E-10</v>
+        <v>-7.091947490861544E-10</v>
       </c>
       <c r="X2">
-        <v>-4.349318257787674E-09</v>
+        <v>-4.349310698182798E-09</v>
       </c>
       <c r="Y2">
-        <v>8.033546563031981E-10</v>
+        <v>8.033387180130823E-10</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -5703,40 +5703,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.8561498318382199</v>
+        <v>0.8561498316503074</v>
       </c>
       <c r="AH2">
-        <v>0.6454597859198975</v>
+        <v>0.6454597859038532</v>
       </c>
       <c r="AI2">
-        <v>0.4396365304738454</v>
+        <v>0.4396365303143212</v>
       </c>
       <c r="AJ2">
-        <v>0.8561498318449055</v>
+        <v>0.8561498316569924</v>
       </c>
       <c r="AK2">
-        <v>0.6454597859015849</v>
+        <v>0.6454597858855414</v>
       </c>
       <c r="AL2">
-        <v>0.4396365305097197</v>
+        <v>0.4396365303501953</v>
       </c>
       <c r="AM2">
-        <v>-3.925473832983799</v>
+        <v>-3.925473815880393</v>
       </c>
       <c r="AN2">
-        <v>-153.8407182628516</v>
+        <v>-153.8407182488145</v>
       </c>
       <c r="AO2">
-        <v>128.6858355487915</v>
+        <v>128.6858355510056</v>
       </c>
       <c r="AP2">
-        <v>-3.925473831981636</v>
+        <v>-3.925473814878264</v>
       </c>
       <c r="AQ2">
-        <v>-153.8407182593601</v>
+        <v>-153.840718245323</v>
       </c>
       <c r="AR2">
-        <v>128.6858355519717</v>
+        <v>128.6858355541859</v>
       </c>
     </row>
   </sheetData>
@@ -5924,40 +5924,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-2.272224128705642E-09</v>
+        <v>-2.272199217439495E-09</v>
       </c>
       <c r="O2">
-        <v>-1.904113527250953E-09</v>
+        <v>-1.904138154672129E-09</v>
       </c>
       <c r="P2">
-        <v>-3.132498569241518E-09</v>
+        <v>-3.132504428703524E-09</v>
       </c>
       <c r="Q2">
-        <v>2.272189102692272E-09</v>
+        <v>2.27219517144389E-09</v>
       </c>
       <c r="R2">
-        <v>1.904149155420491E-09</v>
+        <v>1.904149229065602E-09</v>
       </c>
       <c r="S2">
-        <v>3.132505077898054E-09</v>
+        <v>3.132499222158134E-09</v>
       </c>
       <c r="T2">
-        <v>7.092213860288419E-10</v>
+        <v>7.091993504214106E-10</v>
       </c>
       <c r="U2">
-        <v>4.349328944866132E-09</v>
+        <v>4.349327067606265E-09</v>
       </c>
       <c r="V2">
-        <v>-8.033627840488352E-10</v>
+        <v>-8.033488013211003E-10</v>
       </c>
       <c r="W2">
-        <v>-7.091986571270121E-10</v>
+        <v>-7.091990727495563E-10</v>
       </c>
       <c r="X2">
-        <v>-4.349318257787674E-09</v>
+        <v>-4.349308002264072E-09</v>
       </c>
       <c r="Y2">
-        <v>8.033546563031981E-10</v>
+        <v>8.033553039485708E-10</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -5978,40 +5978,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.8561498318382199</v>
+        <v>0.8561498316503076</v>
       </c>
       <c r="AH2">
-        <v>0.6454597859198975</v>
+        <v>0.6454597859038529</v>
       </c>
       <c r="AI2">
-        <v>0.4396365304738454</v>
+        <v>0.4396365303143211</v>
       </c>
       <c r="AJ2">
-        <v>0.8561498318449055</v>
+        <v>0.8561498316569925</v>
       </c>
       <c r="AK2">
-        <v>0.6454597859015849</v>
+        <v>0.645459785885541</v>
       </c>
       <c r="AL2">
-        <v>0.4396365305097197</v>
+        <v>0.4396365303501953</v>
       </c>
       <c r="AM2">
-        <v>-3.925473832983799</v>
+        <v>-3.925473815880395</v>
       </c>
       <c r="AN2">
-        <v>-153.8407182628516</v>
+        <v>-153.8407182488145</v>
       </c>
       <c r="AO2">
-        <v>128.6858355487915</v>
+        <v>128.6858355510056</v>
       </c>
       <c r="AP2">
-        <v>-3.925473831981636</v>
+        <v>-3.92547381487826</v>
       </c>
       <c r="AQ2">
-        <v>-153.8407182593601</v>
+        <v>-153.840718245323</v>
       </c>
       <c r="AR2">
-        <v>128.6858355519717</v>
+        <v>128.6858355541859</v>
       </c>
     </row>
   </sheetData>
@@ -6199,40 +6199,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-2.44442806755091E-09</v>
+        <v>-2.444451752114444E-09</v>
       </c>
       <c r="O2">
-        <v>-6.11121225032884E-10</v>
+        <v>-6.111180695267663E-10</v>
       </c>
       <c r="P2">
-        <v>-6.111235991430832E-10</v>
+        <v>-6.111046487727096E-10</v>
       </c>
       <c r="Q2">
-        <v>2.444440699522434E-09</v>
+        <v>2.444442278311972E-09</v>
       </c>
       <c r="R2">
-        <v>6.111117518344505E-10</v>
+        <v>6.111164912476148E-10</v>
       </c>
       <c r="S2">
-        <v>6.111125469607825E-10</v>
+        <v>6.111062284612721E-10</v>
       </c>
       <c r="T2">
-        <v>3.159912568484606E-15</v>
+        <v>1.556662409248898E-21</v>
       </c>
       <c r="U2">
-        <v>3.175421801185865E-09</v>
+        <v>3.175428116378735E-09</v>
       </c>
       <c r="V2">
-        <v>-3.175424961308167E-09</v>
+        <v>-3.175428119516285E-09</v>
       </c>
       <c r="W2">
-        <v>-6.317820801733439E-15</v>
+        <v>-3.15790977931337E-15</v>
       </c>
       <c r="X2">
-        <v>-3.175417063817859E-09</v>
+        <v>-3.175428115962294E-09</v>
       </c>
       <c r="Y2">
-        <v>3.175424961724626E-09</v>
+        <v>3.175421803997294E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -6253,40 +6253,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.6666666667165022</v>
+        <v>0.6666666666635035</v>
       </c>
       <c r="AH2">
-        <v>0.3333333331942393</v>
+        <v>0.333333333167029</v>
       </c>
       <c r="AI2">
-        <v>0.3333333335220979</v>
+        <v>0.3333333334964817</v>
       </c>
       <c r="AJ2">
-        <v>0.6666666667439571</v>
+        <v>0.6666666666909594</v>
       </c>
       <c r="AK2">
-        <v>0.3333333331658147</v>
+        <v>0.3333333331386035</v>
       </c>
       <c r="AL2">
-        <v>0.3333333335779807</v>
+        <v>0.3333333335523635</v>
       </c>
       <c r="AM2">
-        <v>-4.558608766268334E-08</v>
+        <v>-3.648678526768855E-11</v>
       </c>
       <c r="AN2">
-        <v>179.9999999565283</v>
+        <v>-179.9999999981412</v>
       </c>
       <c r="AO2">
-        <v>179.9999999526383</v>
+        <v>179.9999999980558</v>
       </c>
       <c r="AP2">
-        <v>-4.419164667159506E-08</v>
+        <v>1.357957064809215E-09</v>
       </c>
       <c r="AQ2">
-        <v>179.9999999701839</v>
+        <v>-179.9999999844855</v>
       </c>
       <c r="AR2">
-        <v>179.9999999417715</v>
+        <v>179.999999987189</v>
       </c>
     </row>
   </sheetData>
@@ -6393,16 +6393,16 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.4028253110876384</v>
+        <v>0.4028253110876379</v>
       </c>
       <c r="O2">
-        <v>0.402825311089443</v>
+        <v>0.4028253110894425</v>
       </c>
       <c r="P2">
-        <v>-25.8807585799728</v>
+        <v>-25.88075857997278</v>
       </c>
       <c r="Q2">
-        <v>-25.88075857298006</v>
+        <v>-25.88075857298004</v>
       </c>
     </row>
   </sheetData>
@@ -6590,40 +6590,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-2.44442806755091E-09</v>
+        <v>-2.444451752114444E-09</v>
       </c>
       <c r="O2">
-        <v>-6.11121225032884E-10</v>
+        <v>-6.111180695267663E-10</v>
       </c>
       <c r="P2">
-        <v>-6.111235991430832E-10</v>
+        <v>-6.111046487727096E-10</v>
       </c>
       <c r="Q2">
-        <v>2.444440699522434E-09</v>
+        <v>2.444442278311972E-09</v>
       </c>
       <c r="R2">
-        <v>6.111117518344505E-10</v>
+        <v>6.111164912476148E-10</v>
       </c>
       <c r="S2">
-        <v>6.111125469607825E-10</v>
+        <v>6.111062284612721E-10</v>
       </c>
       <c r="T2">
-        <v>3.159912568484606E-15</v>
+        <v>1.556662409248898E-21</v>
       </c>
       <c r="U2">
-        <v>3.175421801185865E-09</v>
+        <v>3.175428116378735E-09</v>
       </c>
       <c r="V2">
-        <v>-3.175424961308167E-09</v>
+        <v>-3.175428119516285E-09</v>
       </c>
       <c r="W2">
-        <v>-6.317820801733439E-15</v>
+        <v>-3.15790977931337E-15</v>
       </c>
       <c r="X2">
-        <v>-3.175417063817859E-09</v>
+        <v>-3.175428115962294E-09</v>
       </c>
       <c r="Y2">
-        <v>3.175424961724626E-09</v>
+        <v>3.175421803997294E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -6644,40 +6644,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.6666666667165022</v>
+        <v>0.6666666666635035</v>
       </c>
       <c r="AH2">
-        <v>0.3333333331942393</v>
+        <v>0.333333333167029</v>
       </c>
       <c r="AI2">
-        <v>0.3333333335220979</v>
+        <v>0.3333333334964817</v>
       </c>
       <c r="AJ2">
-        <v>0.6666666667439571</v>
+        <v>0.6666666666909594</v>
       </c>
       <c r="AK2">
-        <v>0.3333333331658147</v>
+        <v>0.3333333331386035</v>
       </c>
       <c r="AL2">
-        <v>0.3333333335779807</v>
+        <v>0.3333333335523635</v>
       </c>
       <c r="AM2">
-        <v>-4.558608766268334E-08</v>
+        <v>-3.648678526768855E-11</v>
       </c>
       <c r="AN2">
-        <v>179.9999999565283</v>
+        <v>-179.9999999981412</v>
       </c>
       <c r="AO2">
-        <v>179.9999999526383</v>
+        <v>179.9999999980558</v>
       </c>
       <c r="AP2">
-        <v>-4.419164667159506E-08</v>
+        <v>1.357957064809215E-09</v>
       </c>
       <c r="AQ2">
-        <v>179.9999999701839</v>
+        <v>-179.9999999844855</v>
       </c>
       <c r="AR2">
-        <v>179.9999999417715</v>
+        <v>179.999999987189</v>
       </c>
     </row>
   </sheetData>
@@ -6865,40 +6865,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-1.94165869280456E-09</v>
+        <v>-1.941671396935362E-09</v>
       </c>
       <c r="O2">
-        <v>-1.538359414715884E-09</v>
+        <v>-1.538354363321492E-09</v>
       </c>
       <c r="P2">
-        <v>-2.50638644914713E-09</v>
+        <v>-2.506381376515883E-09</v>
       </c>
       <c r="Q2">
-        <v>1.941670489756954E-09</v>
+        <v>1.941666072602194E-09</v>
       </c>
       <c r="R2">
-        <v>1.538350264313319E-09</v>
+        <v>1.538352971766674E-09</v>
       </c>
       <c r="S2">
-        <v>2.506384665092787E-09</v>
+        <v>2.506386167012948E-09</v>
       </c>
       <c r="T2">
-        <v>5.588928756925769E-10</v>
+        <v>5.588937173775607E-10</v>
       </c>
       <c r="U2">
-        <v>3.623732301603949E-09</v>
+        <v>3.623739001725343E-09</v>
       </c>
       <c r="V2">
-        <v>-8.292813704951605E-10</v>
+        <v>-8.292816836296678E-10</v>
       </c>
       <c r="W2">
-        <v>-5.588936578611215E-10</v>
+        <v>-5.588915414241487E-10</v>
       </c>
       <c r="X2">
-        <v>-3.62373644723324E-09</v>
+        <v>-3.623744043764988E-09</v>
       </c>
       <c r="Y2">
-        <v>8.29283390062061E-10</v>
+        <v>8.292871154073853E-10</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -6919,40 +6919,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.7679592757634635</v>
+        <v>0.7679592756099298</v>
       </c>
       <c r="AH2">
-        <v>0.5655462792981835</v>
+        <v>0.5655462792825745</v>
       </c>
       <c r="AI2">
-        <v>0.3792589158036762</v>
+        <v>0.3792589156706165</v>
       </c>
       <c r="AJ2">
-        <v>0.7679592757791751</v>
+        <v>0.7679592756256418</v>
       </c>
       <c r="AK2">
-        <v>0.5655462792901989</v>
+        <v>0.5655462792745894</v>
       </c>
       <c r="AL2">
-        <v>0.3792589158628378</v>
+        <v>0.3792589157297778</v>
       </c>
       <c r="AM2">
-        <v>-3.793471542479584</v>
+        <v>-3.793471525611851</v>
       </c>
       <c r="AN2">
-        <v>-155.6266320234988</v>
+        <v>-155.6266320097133</v>
       </c>
       <c r="AO2">
-        <v>131.4656840089738</v>
+        <v>131.4656840130515</v>
       </c>
       <c r="AP2">
-        <v>-3.793471541238289</v>
+        <v>-3.793471524370559</v>
       </c>
       <c r="AQ2">
-        <v>-155.6266320174186</v>
+        <v>-155.6266320036331</v>
       </c>
       <c r="AR2">
-        <v>131.4656840109181</v>
+        <v>131.4656840149958</v>
       </c>
     </row>
   </sheetData>
@@ -7140,40 +7140,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-1.94165869280456E-09</v>
+        <v>-1.941671396935362E-09</v>
       </c>
       <c r="O2">
-        <v>-1.538359414715884E-09</v>
+        <v>-1.538354363321492E-09</v>
       </c>
       <c r="P2">
-        <v>-2.50638644914713E-09</v>
+        <v>-2.506381376515883E-09</v>
       </c>
       <c r="Q2">
-        <v>1.941670489756954E-09</v>
+        <v>1.941666072602194E-09</v>
       </c>
       <c r="R2">
-        <v>1.538350264313319E-09</v>
+        <v>1.538352971766674E-09</v>
       </c>
       <c r="S2">
-        <v>2.506384665092787E-09</v>
+        <v>2.506386167012948E-09</v>
       </c>
       <c r="T2">
-        <v>5.588928756925769E-10</v>
+        <v>5.588937173775607E-10</v>
       </c>
       <c r="U2">
-        <v>3.623732301603949E-09</v>
+        <v>3.623739001725343E-09</v>
       </c>
       <c r="V2">
-        <v>-8.292813704951605E-10</v>
+        <v>-8.292816836296678E-10</v>
       </c>
       <c r="W2">
-        <v>-5.588936578611215E-10</v>
+        <v>-5.588915414241487E-10</v>
       </c>
       <c r="X2">
-        <v>-3.62373644723324E-09</v>
+        <v>-3.623744043764988E-09</v>
       </c>
       <c r="Y2">
-        <v>8.29283390062061E-10</v>
+        <v>8.292871154073853E-10</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -7194,40 +7194,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.7679592757634635</v>
+        <v>0.7679592756099298</v>
       </c>
       <c r="AH2">
-        <v>0.5655462792981835</v>
+        <v>0.5655462792825745</v>
       </c>
       <c r="AI2">
-        <v>0.3792589158036762</v>
+        <v>0.3792589156706165</v>
       </c>
       <c r="AJ2">
-        <v>0.7679592757791751</v>
+        <v>0.7679592756256418</v>
       </c>
       <c r="AK2">
-        <v>0.5655462792901989</v>
+        <v>0.5655462792745894</v>
       </c>
       <c r="AL2">
-        <v>0.3792589158628378</v>
+        <v>0.3792589157297778</v>
       </c>
       <c r="AM2">
-        <v>-3.793471542479584</v>
+        <v>-3.793471525611851</v>
       </c>
       <c r="AN2">
-        <v>-155.6266320234988</v>
+        <v>-155.6266320097133</v>
       </c>
       <c r="AO2">
-        <v>131.4656840089738</v>
+        <v>131.4656840130515</v>
       </c>
       <c r="AP2">
-        <v>-3.793471541238289</v>
+        <v>-3.793471524370559</v>
       </c>
       <c r="AQ2">
-        <v>-155.6266320174186</v>
+        <v>-155.6266320036331</v>
       </c>
       <c r="AR2">
-        <v>131.4656840109181</v>
+        <v>131.4656840149958</v>
       </c>
     </row>
   </sheetData>
@@ -7334,16 +7334,16 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.4028253110876387</v>
+        <v>0.4028253110876389</v>
       </c>
       <c r="O2">
-        <v>0.4028253110894434</v>
+        <v>0.4028253110894437</v>
       </c>
       <c r="P2">
-        <v>-25.88075857997276</v>
+        <v>-25.88075857997272</v>
       </c>
       <c r="Q2">
-        <v>-25.88075857298002</v>
+        <v>-25.88075857297997</v>
       </c>
     </row>
   </sheetData>
@@ -7682,16 +7682,16 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.3354590830466711</v>
+        <v>0.3354590830466712</v>
       </c>
       <c r="O2">
         <v>0.3354590830702975</v>
       </c>
       <c r="P2">
-        <v>-27.02488376071815</v>
+        <v>-27.02488376071819</v>
       </c>
       <c r="Q2">
-        <v>-27.02488374970884</v>
+        <v>-27.0248837497089</v>
       </c>
     </row>
   </sheetData>
@@ -7798,16 +7798,16 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.3354590830466711</v>
+        <v>0.3354590830466712</v>
       </c>
       <c r="O2">
         <v>0.3354590830702975</v>
       </c>
       <c r="P2">
-        <v>-27.02488376071815</v>
+        <v>-27.02488376071819</v>
       </c>
       <c r="Q2">
-        <v>-27.02488374970884</v>
+        <v>-27.0248837497089</v>
       </c>
     </row>
   </sheetData>
@@ -7992,40 +7992,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-1.563194052505438E-14</v>
+        <v>-1.563194052506517E-14</v>
       </c>
       <c r="O2">
-        <v>5.210612506905471E-15</v>
+        <v>-1.042133752427119E-14</v>
       </c>
       <c r="P2">
-        <v>-1.042134522547605E-14</v>
+        <v>-1.042133823101581E-14</v>
       </c>
       <c r="Q2">
-        <v>-1.168742183302731E-26</v>
+        <v>5.210646841688491E-15</v>
       </c>
       <c r="R2">
-        <v>4.625822325666277E-19</v>
+        <v>1.302708919413955E-14</v>
       </c>
       <c r="S2">
-        <v>5.211126632729633E-15</v>
+        <v>4.727896244586341E-19</v>
       </c>
       <c r="T2">
-        <v>1.042129368339491E-14</v>
+        <v>5.210646841688187E-15</v>
       </c>
       <c r="U2">
-        <v>5.76340267785982E-09</v>
+        <v>5.76338444060293E-09</v>
       </c>
       <c r="V2">
-        <v>-5.76340268204086E-09</v>
+        <v>-5.763387050089313E-09</v>
       </c>
       <c r="W2">
-        <v>-1.042129368337738E-14</v>
+        <v>-1.042129368337668E-14</v>
       </c>
       <c r="X2">
-        <v>-5.763413098667596E-09</v>
+        <v>-5.763389650763873E-09</v>
       </c>
       <c r="Y2">
-        <v>5.763397471879912E-09</v>
+        <v>5.763381839928366E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -8046,40 +8046,40 @@
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.100000023808833</v>
+        <v>1.100000023808765</v>
       </c>
       <c r="AG2">
-        <v>0.5500000117050743</v>
+        <v>0.550000011705747</v>
       </c>
       <c r="AH2">
-        <v>0.5500000121040698</v>
+        <v>0.5500000121030185</v>
       </c>
       <c r="AI2">
-        <v>1.100000023808833</v>
+        <v>1.100000023808765</v>
       </c>
       <c r="AJ2">
-        <v>0.5500000116587047</v>
+        <v>0.550000011659378</v>
       </c>
       <c r="AK2">
-        <v>0.5500000121504387</v>
+        <v>0.5500000121493877</v>
       </c>
       <c r="AL2">
-        <v>-6.426806457872223E-11</v>
+        <v>6.692774592374453E-13</v>
       </c>
       <c r="AM2">
-        <v>-179.9999999996514</v>
+        <v>-179.9999999995568</v>
       </c>
       <c r="AN2">
-        <v>179.9999999994803</v>
+        <v>179.9999999995499</v>
       </c>
       <c r="AO2">
-        <v>-6.425689216393618E-11</v>
+        <v>6.658785920483112E-13</v>
       </c>
       <c r="AP2">
-        <v>-179.9999999953941</v>
+        <v>-179.9999999952994</v>
       </c>
       <c r="AQ2">
-        <v>179.999999995223</v>
+        <v>179.9999999952925</v>
       </c>
     </row>
   </sheetData>
